--- a/output/resumo_contratos.xlsx
+++ b/output/resumo_contratos.xlsx
@@ -448,16 +448,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19764.2</v>
+        <v>59292.6</v>
       </c>
       <c r="C2" t="n">
-        <v>168643.63</v>
+        <v>262471.02</v>
       </c>
       <c r="D2" t="n">
         <v>2083.33</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
@@ -465,16 +465,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>57585.85</v>
+        <v>172757.55</v>
       </c>
       <c r="C3" t="n">
-        <v>472294.53</v>
+        <v>743601.54</v>
       </c>
       <c r="D3" t="n">
         <v>4166.67</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
@@ -482,16 +482,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5266.47</v>
+        <v>15799.41</v>
       </c>
       <c r="C4" t="n">
-        <v>46349.49</v>
+        <v>71655.17999999999</v>
       </c>
       <c r="D4" t="n">
         <v>1388.89</v>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
@@ -499,16 +499,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26124.17</v>
+        <v>76582.14999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>192310.94</v>
+        <v>305388.23</v>
       </c>
       <c r="D5" t="n">
         <v>2500</v>
       </c>
       <c r="E5" t="n">
-        <v>84</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
@@ -516,16 +516,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16705.84</v>
+        <v>50117.52</v>
       </c>
       <c r="C6" t="n">
-        <v>134727.8</v>
+        <v>213420.15</v>
       </c>
       <c r="D6" t="n">
         <v>1875</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7">
@@ -533,16 +533,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30520.17</v>
+        <v>88910.2</v>
       </c>
       <c r="C7" t="n">
-        <v>233871.69</v>
+        <v>365248.1</v>
       </c>
       <c r="D7" t="n">
         <v>5333.33</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
@@ -550,16 +550,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4606.44</v>
+        <v>13819.32</v>
       </c>
       <c r="C8" t="n">
-        <v>40438.8</v>
+        <v>62743.26</v>
       </c>
       <c r="D8" t="n">
         <v>3125</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -567,16 +567,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20898.22</v>
+        <v>62694.66</v>
       </c>
       <c r="C9" t="n">
-        <v>171832.25</v>
+        <v>271049.07</v>
       </c>
       <c r="D9" t="n">
         <v>4166.67</v>
       </c>
       <c r="E9" t="n">
-        <v>39</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -584,16 +584,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44040.26</v>
+        <v>132120.78</v>
       </c>
       <c r="C10" t="n">
-        <v>339497.29</v>
+        <v>545337.51</v>
       </c>
       <c r="D10" t="n">
         <v>4375</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -601,16 +601,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2651.35</v>
+        <v>7954.05</v>
       </c>
       <c r="C11" t="n">
-        <v>22500.62</v>
+        <v>35278.92</v>
       </c>
       <c r="D11" t="n">
         <v>1666.67</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -618,16 +618,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>91927.34</v>
+        <v>270792.98</v>
       </c>
       <c r="C12" t="n">
-        <v>602385.2</v>
+        <v>992475.46</v>
       </c>
       <c r="D12" t="n">
         <v>5952.38</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13">
@@ -635,16 +635,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>28382.71</v>
+        <v>85148.13</v>
       </c>
       <c r="C13" t="n">
-        <v>203255.37</v>
+        <v>333719.55</v>
       </c>
       <c r="D13" t="n">
         <v>2000</v>
       </c>
       <c r="E13" t="n">
-        <v>66</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14">
@@ -652,16 +652,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>17963.34</v>
+        <v>53890.02</v>
       </c>
       <c r="C14" t="n">
-        <v>133965.82</v>
+        <v>217304.94</v>
       </c>
       <c r="D14" t="n">
         <v>1979.17</v>
       </c>
       <c r="E14" t="n">
-        <v>51</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
@@ -669,16 +669,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>85009</v>
+        <v>255027</v>
       </c>
       <c r="C15" t="n">
-        <v>572399.39</v>
+        <v>955880.9399999999</v>
       </c>
       <c r="D15" t="n">
         <v>3819.44</v>
       </c>
       <c r="E15" t="n">
-        <v>78</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16">
@@ -686,16 +686,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6319.76</v>
+        <v>18959.28</v>
       </c>
       <c r="C16" t="n">
-        <v>48575.92</v>
+        <v>78062.03999999999</v>
       </c>
       <c r="D16" t="n">
         <v>1666.67</v>
       </c>
       <c r="E16" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17">
@@ -703,16 +703,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>43241.14</v>
+        <v>126759.89</v>
       </c>
       <c r="C17" t="n">
-        <v>285550.1</v>
+        <v>468746.41</v>
       </c>
       <c r="D17" t="n">
         <v>5666.67</v>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18">
@@ -720,16 +720,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11514.54</v>
+        <v>34543.62</v>
       </c>
       <c r="C18" t="n">
-        <v>84574.33</v>
+        <v>137574.09</v>
       </c>
       <c r="D18" t="n">
         <v>2444.44</v>
       </c>
       <c r="E18" t="n">
-        <v>39</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
@@ -737,16 +737,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>32505.92</v>
+        <v>97517.75999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>223843.35</v>
+        <v>371516.28</v>
       </c>
       <c r="D19" t="n">
         <v>3229.17</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20">
@@ -754,16 +754,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>58406.19</v>
+        <v>175218.57</v>
       </c>
       <c r="C20" t="n">
-        <v>382158.28</v>
+        <v>643882.77</v>
       </c>
       <c r="D20" t="n">
         <v>3666.67</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21">
@@ -771,16 +771,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17463.78</v>
+        <v>52391.34</v>
       </c>
       <c r="C21" t="n">
-        <v>120328.56</v>
+        <v>199563.54</v>
       </c>
       <c r="D21" t="n">
         <v>2291.67</v>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
